--- a/docs/sample-output/01-garden-multifamily/proforma.xlsx
+++ b/docs/sample-output/01-garden-multifamily/proforma.xlsx
@@ -270,7 +270,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 5 at -4.68% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 5 at -4.20% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   Cedar Hollow — garden multifamily · 5-Year Before-Tax</t>
@@ -1088,7 +1088,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>66654800.31</v>
+        <v>66218599.1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="8">
-        <v>0.04620486425098406</v>
+        <v>0.046509229157039055</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1104,7 +1104,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="7">
-        <v>23762436.310514994</v>
+        <v>23606930.57915</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>-0.0467976372113921</v>
+        <v>-0.042020093473425314</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1128,7 +1128,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="9">
-        <v>0.7806214994764685</v>
+        <v>0.8015063807295657</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1144,7 +1144,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="8">
-        <v>-0.0467976372113921</v>
+        <v>-0.042020093473425314</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1159,7 +1159,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="7">
-        <v>66654800.31</v>
+        <v>66218599.1</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1175,7 +1175,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="7">
-        <v>433256.20201500005</v>
+        <v>430420.89415</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1183,7 +1183,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="7">
-        <v>66654800.31</v>
+        <v>66218599.1</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1191,7 +1191,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="7">
-        <v>-43325620.201500006</v>
+        <v>-43042089.415</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1199,7 +1199,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>23762436.310514994</v>
+        <v>23606930.57915</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1207,7 +1207,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>12.857793269675927</v>
+        <v>12.773649517746914</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1215,7 +1215,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="13">
-        <v>264.50317583333333</v>
+        <v>262.77221865079366</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1223,7 +1223,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="7">
-        <v>277728.334625</v>
+        <v>275910.82958333334</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1238,7 +1238,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="7">
-        <v>43325620.201500006</v>
+        <v>43042089.415</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1270,7 +1270,7 @@
         <v>44</v>
       </c>
       <c r="B37" s="13">
-        <v>292537.6902988086</v>
+        <v>290623.27012373524</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1278,7 +1278,7 @@
         <v>45</v>
       </c>
       <c r="B38" s="7">
-        <v>3510452.2835857035</v>
+        <v>3487479.2414848227</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1513,19 +1513,19 @@
         <v>62</v>
       </c>
       <c r="B13" s="17">
-        <v>-3510452.2835857035</v>
+        <v>-3487479.2414848227</v>
       </c>
       <c r="C13" s="17">
-        <v>-3510452.2835857035</v>
+        <v>-3487479.2414848227</v>
       </c>
       <c r="D13" s="17">
-        <v>-3510452.2835857035</v>
+        <v>-3487479.2414848227</v>
       </c>
       <c r="E13" s="17">
-        <v>-3510452.2835857035</v>
+        <v>-3487479.2414848227</v>
       </c>
       <c r="F13" s="17">
-        <v>-3510452.2835857035</v>
+        <v>-3487479.2414848227</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1533,19 +1533,19 @@
         <v>63</v>
       </c>
       <c r="B14" s="19">
-        <v>-430676.28358570347</v>
+        <v>-407703.2414848227</v>
       </c>
       <c r="C14" s="19">
-        <v>-338283.0035857037</v>
+        <v>-315309.9614848229</v>
       </c>
       <c r="D14" s="19">
-        <v>-243117.92518570367</v>
+        <v>-220144.8830848229</v>
       </c>
       <c r="E14" s="19">
-        <v>-145097.89443370327</v>
+        <v>-122124.85233282251</v>
       </c>
       <c r="F14" s="19">
-        <v>-44137.26275914349</v>
+        <v>-21164.220658262726</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1689,19 +1689,19 @@
         <v>70</v>
       </c>
       <c r="B9" s="17">
-        <v>-42610271.21327186</v>
+        <v>-42331421.80144833</v>
       </c>
       <c r="C9" s="17">
-        <v>-41847013.97847391</v>
+        <v>-41573159.46165888</v>
       </c>
       <c r="D9" s="17">
-        <v>-41032639.993107215</v>
+        <v>-40764114.888669945</v>
       </c>
       <c r="E9" s="17">
-        <v>-40163725.873717815</v>
+        <v>-39900887.102275334</v>
       </c>
       <c r="F9" s="17">
-        <v>-39236618.96652175</v>
+        <v>-38979847.35232582</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1709,19 +1709,19 @@
         <v>71</v>
       </c>
       <c r="B10" s="19">
-        <v>9799328.786728144</v>
+        <v>10078178.19855167</v>
       </c>
       <c r="C10" s="19">
-        <v>12134836.02152609</v>
+        <v>12408690.53834112</v>
       </c>
       <c r="D10" s="19">
-        <v>14568960.006892785</v>
+        <v>14837485.111330055</v>
       </c>
       <c r="E10" s="19">
-        <v>17106074.126282185</v>
+        <v>17368912.897724666</v>
       </c>
       <c r="F10" s="19">
-        <v>19750781.033478253</v>
+        <v>20007552.64767418</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1759,19 +1759,19 @@
         <v>73</v>
       </c>
       <c r="B13" s="22">
-        <v>0.7723729555769986</v>
+        <v>0.7673184056237009</v>
       </c>
       <c r="C13" s="22">
-        <v>0.7364449954855237</v>
+        <v>0.7316255646773117</v>
       </c>
       <c r="D13" s="22">
-        <v>0.701077091188956</v>
+        <v>0.6964891144182263</v>
       </c>
       <c r="E13" s="22">
-        <v>0.6662418863001429</v>
+        <v>0.6618818774844957</v>
       </c>
       <c r="F13" s="22">
-        <v>0.6319110185937278</v>
+        <v>0.6277756772583557</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1779,19 +1779,19 @@
         <v>74</v>
       </c>
       <c r="B14" s="23">
-        <v>0.8773160126404581</v>
+        <v>0.8830951488871831</v>
       </c>
       <c r="C14" s="23">
-        <v>0.9036354930196718</v>
+        <v>0.9095880033537985</v>
       </c>
       <c r="D14" s="23">
-        <v>0.9307445578102619</v>
+        <v>0.9368756434544125</v>
       </c>
       <c r="E14" s="23">
-        <v>0.9586668945445699</v>
+        <v>0.964981912758045</v>
       </c>
       <c r="F14" s="23">
-        <v>0.9874269013809069</v>
+        <v>0.9939313701407863</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1799,19 +1799,19 @@
         <v>75</v>
       </c>
       <c r="B15" s="22">
-        <v>0.07108440653997546</v>
+        <v>0.07155266024159855</v>
       </c>
       <c r="C15" s="22">
-        <v>0.07321693873617471</v>
+        <v>0.0736992400488465</v>
       </c>
       <c r="D15" s="22">
-        <v>0.07541344689825996</v>
+        <v>0.07591021725031188</v>
       </c>
       <c r="E15" s="22">
-        <v>0.07767585030520777</v>
+        <v>0.07818752376782126</v>
       </c>
       <c r="F15" s="22">
-        <v>0.080006125814364</v>
+        <v>0.0805331494808559</v>
       </c>
     </row>
   </sheetData>
@@ -1887,19 +1887,19 @@
         <v>77</v>
       </c>
       <c r="B5" s="22">
-        <v>-0.018124247781576466</v>
+        <v>-0.017270489279318357</v>
       </c>
       <c r="C5" s="22">
-        <v>-0.014236040411227184</v>
+        <v>-0.013356669153901332</v>
       </c>
       <c r="D5" s="22">
-        <v>-0.010231186819767417</v>
+        <v>-0.009325434424721791</v>
       </c>
       <c r="E5" s="22">
-        <v>-0.006106187620563837</v>
+        <v>-0.005173262653666845</v>
       </c>
       <c r="F5" s="22">
-        <v>-0.001857438445384177</v>
+        <v>-0.0008965257294802776</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1907,19 +1907,19 @@
         <v>78</v>
       </c>
       <c r="B6" s="22">
-        <v>-0.043949569706141084</v>
+        <v>-0.04045406158261952</v>
       </c>
       <c r="C6" s="22">
-        <v>-0.02787701481796874</v>
+        <v>-0.025410413815265938</v>
       </c>
       <c r="D6" s="22">
-        <v>-0.016687390525520082</v>
+        <v>-0.014837075247793714</v>
       </c>
       <c r="E6" s="22">
-        <v>-0.008482243989038452</v>
+        <v>-0.007031231778980302</v>
       </c>
       <c r="F6" s="22">
-        <v>-0.0022347097405580724</v>
+        <v>-0.0010578115690088165</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1927,19 +1927,19 @@
         <v>79</v>
       </c>
       <c r="B7" s="24">
-        <v>0.39426312945010467</v>
+        <v>0.4096455879616962</v>
       </c>
       <c r="C7" s="24">
-        <v>0.4783127700304547</v>
+        <v>0.4950104502655014</v>
       </c>
       <c r="D7" s="24">
-        <v>0.5705173752969382</v>
+        <v>0.588569826080959</v>
       </c>
       <c r="E7" s="24">
-        <v>0.6711811369457056</v>
+        <v>0.6906289618921059</v>
       </c>
       <c r="F7" s="24">
-        <v>0.7806214994764685</v>
+        <v>0.8015063807295657</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1947,19 +1947,19 @@
         <v>80</v>
       </c>
       <c r="B8" s="22">
-        <v>-0.16751118086105107</v>
+        <v>-0.16202733440167721</v>
       </c>
       <c r="C8" s="22">
-        <v>-0.050616489593576744</v>
+        <v>-0.047416569119879924</v>
       </c>
       <c r="D8" s="22">
-        <v>-0.00811428697746398</v>
+        <v>-0.005833177713718737</v>
       </c>
       <c r="E8" s="22">
-        <v>0.013822962824061771</v>
+        <v>0.015612403188792466</v>
       </c>
       <c r="F8" s="22">
-        <v>0.027195296255604663</v>
+        <v>0.02867923022107996</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1987,19 +1987,19 @@
         <v>82</v>
       </c>
       <c r="B10" s="25">
-        <v>-0.6057368705495801</v>
+        <v>-0.5903544120385642</v>
       </c>
       <c r="C10" s="25">
-        <v>-0.3044209812507864</v>
+        <v>-0.2928451168822346</v>
       </c>
       <c r="D10" s="25">
-        <v>-0.16679625391212322</v>
+        <v>-0.1585725299066838</v>
       </c>
       <c r="E10" s="25">
-        <v>-0.09218323583413604</v>
+        <v>-0.08605538022093155</v>
       </c>
       <c r="F10" s="25">
-        <v>-0.0467976372113921</v>
+        <v>-0.042020093473425314</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2007,19 +2007,19 @@
         <v>83</v>
       </c>
       <c r="B11" s="22">
-        <v>-0.43820000000000003</v>
+        <v>-0.4284</v>
       </c>
       <c r="C11" s="22">
-        <v>-0.2538</v>
+        <v>-0.2454</v>
       </c>
       <c r="D11" s="22">
-        <v>-0.1587</v>
+        <v>-0.1528</v>
       </c>
       <c r="E11" s="22">
-        <v>-0.10600000000000001</v>
+        <v>-0.1017</v>
       </c>
       <c r="F11" s="22">
-        <v>-0.074</v>
+        <v>-0.0707</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2113,19 +2113,19 @@
         <v>19</v>
       </c>
       <c r="B6" s="19">
-        <v>59989320</v>
+        <v>59596739</v>
       </c>
       <c r="C6" s="19">
-        <v>63322060</v>
+        <v>62907669</v>
       </c>
       <c r="D6" s="19">
-        <v>66654800</v>
+        <v>66218599</v>
       </c>
       <c r="E6" s="19">
-        <v>69987540</v>
+        <v>69529529</v>
       </c>
       <c r="F6" s="19">
-        <v>73320280</v>
+        <v>72840459</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2133,19 +2133,19 @@
         <v>20</v>
       </c>
       <c r="B7" s="22">
-        <v>0.05133873829541658</v>
+        <v>0.05167692145034983</v>
       </c>
       <c r="C7" s="22">
-        <v>0.04863669943776308</v>
+        <v>0.04895708343604339</v>
       </c>
       <c r="D7" s="22">
-        <v>0.04620486446587493</v>
+        <v>0.046509229227274955</v>
       </c>
       <c r="E7" s="22">
-        <v>0.044004632824642786</v>
+        <v>0.04429450399412313</v>
       </c>
       <c r="F7" s="22">
-        <v>0.042004422241704475</v>
+        <v>0.042281117421294666</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2153,19 +2153,19 @@
         <v>92</v>
       </c>
       <c r="B8" s="17">
-        <v>38993058</v>
+        <v>38737880.35</v>
       </c>
       <c r="C8" s="17">
-        <v>41159339</v>
+        <v>40889984.85</v>
       </c>
       <c r="D8" s="17">
-        <v>43325620</v>
+        <v>43042089.35</v>
       </c>
       <c r="E8" s="17">
-        <v>45491901</v>
+        <v>45194193.85</v>
       </c>
       <c r="F8" s="17">
-        <v>47658182</v>
+        <v>47346298.35</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2173,19 +2173,19 @@
         <v>21</v>
       </c>
       <c r="B9" s="17">
-        <v>21386192.58</v>
+        <v>21246237.453499995</v>
       </c>
       <c r="C9" s="17">
-        <v>22574314.39</v>
+        <v>22426583.998499997</v>
       </c>
       <c r="D9" s="17">
-        <v>23762436.200000003</v>
+        <v>23606930.5435</v>
       </c>
       <c r="E9" s="17">
-        <v>24950558.010000005</v>
+        <v>24787277.0885</v>
       </c>
       <c r="F9" s="17">
-        <v>26138679.819999993</v>
+        <v>25967623.633500002</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2193,19 +2193,19 @@
         <v>93</v>
       </c>
       <c r="B10" s="22">
-        <v>0.05133873829541658</v>
+        <v>0.05167692145034983</v>
       </c>
       <c r="C10" s="22">
-        <v>0.04863669943776308</v>
+        <v>0.04895708343604339</v>
       </c>
       <c r="D10" s="22">
-        <v>0.04620486446587493</v>
+        <v>0.046509229227274955</v>
       </c>
       <c r="E10" s="22">
-        <v>0.044004632824642786</v>
+        <v>0.04429450399412313</v>
       </c>
       <c r="F10" s="22">
-        <v>0.042004422241704475</v>
+        <v>0.042281117421294666</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2213,19 +2213,19 @@
         <v>94</v>
       </c>
       <c r="B11" s="22">
-        <v>0.05287890044427908</v>
+        <v>0.053227229093860316</v>
       </c>
       <c r="C11" s="22">
-        <v>0.05009580042089597</v>
+        <v>0.05042579593912468</v>
       </c>
       <c r="D11" s="22">
-        <v>0.04759101039985117</v>
+        <v>0.0479045061040932</v>
       </c>
       <c r="E11" s="22">
-        <v>0.04532477180938207</v>
+        <v>0.04562333911394682</v>
       </c>
       <c r="F11" s="22">
-        <v>0.04326455490895561</v>
+        <v>0.04354955094393351</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2233,19 +2233,19 @@
         <v>95</v>
       </c>
       <c r="B12" s="22">
-        <v>0.05446526745760745</v>
+        <v>0.05482404596667612</v>
       </c>
       <c r="C12" s="22">
-        <v>0.05159867443352285</v>
+        <v>0.05193856981729843</v>
       </c>
       <c r="D12" s="22">
-        <v>0.049018740711846705</v>
+        <v>0.04934164128721599</v>
       </c>
       <c r="E12" s="22">
-        <v>0.04668451496366353</v>
+        <v>0.04699203928736523</v>
       </c>
       <c r="F12" s="22">
-        <v>0.04456249155622428</v>
+        <v>0.04485603747225151</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2253,19 +2253,19 @@
         <v>96</v>
       </c>
       <c r="B13" s="22">
-        <v>0.05609922548133568</v>
+        <v>0.056468767345676414</v>
       </c>
       <c r="C13" s="22">
-        <v>0.05314663466652854</v>
+        <v>0.05349672691181739</v>
       </c>
       <c r="D13" s="22">
-        <v>0.05048930293320211</v>
+        <v>0.05082189052583248</v>
       </c>
       <c r="E13" s="22">
-        <v>0.04808505041257344</v>
+        <v>0.04840180046598619</v>
       </c>
       <c r="F13" s="22">
-        <v>0.04589936630291101</v>
+        <v>0.04620171859641906</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2273,19 +2273,19 @@
         <v>97</v>
       </c>
       <c r="B14" s="22">
-        <v>0.057782202245775745</v>
+        <v>0.058162830366046706</v>
       </c>
       <c r="C14" s="22">
-        <v>0.054741033706524396</v>
+        <v>0.0551016287191719</v>
       </c>
       <c r="D14" s="22">
-        <v>0.05200398202119817</v>
+        <v>0.05234654724160745</v>
       </c>
       <c r="E14" s="22">
-        <v>0.04952760192495064</v>
+        <v>0.04985385447996577</v>
       </c>
       <c r="F14" s="22">
-        <v>0.04727634729199834</v>
+        <v>0.04758777015431163</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2293,19 +2293,19 @@
         <v>98</v>
       </c>
       <c r="B15" s="22">
-        <v>-0.0037234790734907873</v>
+        <v>-0.00277485872304692</v>
       </c>
       <c r="C15" s="22">
-        <v>-0.011302830707862485</v>
+        <v>-0.010404137865561493</v>
       </c>
       <c r="D15" s="22">
-        <v>-0.018124247178796994</v>
+        <v>-0.017270489082303216</v>
       </c>
       <c r="E15" s="22">
-        <v>-0.02429600493821391</v>
+        <v>-0.02348290207852153</v>
       </c>
       <c r="F15" s="22">
-        <v>-0.029906693810411156</v>
+        <v>-0.029130550249148342</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2313,19 +2313,19 @@
         <v>99</v>
       </c>
       <c r="B16" s="22">
-        <v>0.0005967513581010618</v>
+        <v>0.001573830319058246</v>
       </c>
       <c r="C16" s="22">
-        <v>-0.0072099808253017865</v>
+        <v>-0.006284327197731764</v>
       </c>
       <c r="D16" s="22">
-        <v>-0.014236039790364328</v>
+        <v>-0.01335666895097574</v>
       </c>
       <c r="E16" s="22">
-        <v>-0.020592950282563752</v>
+        <v>-0.0197554543370806</v>
       </c>
       <c r="F16" s="22">
-        <v>-0.026371959820926914</v>
+        <v>-0.02557253195282622</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2333,19 +2333,19 @@
         <v>100</v>
       </c>
       <c r="B17" s="22">
-        <v>0.005046588702640676</v>
+        <v>0.0060529800324265765</v>
       </c>
       <c r="C17" s="22">
-        <v>-0.0029943454462642576</v>
+        <v>-0.002040922209867134</v>
       </c>
       <c r="D17" s="22">
-        <v>-0.010231186180278677</v>
+        <v>-0.009325434215708429</v>
       </c>
       <c r="E17" s="22">
-        <v>-0.016778803987244083</v>
+        <v>-0.015916183163396436</v>
       </c>
       <c r="F17" s="22">
-        <v>-0.02273118381175814</v>
+        <v>-0.021907773107614426</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2353,19 +2353,19 @@
         <v>101</v>
       </c>
       <c r="B18" s="22">
-        <v>0.009629921167516499</v>
+        <v>0.010666504237195977</v>
       </c>
       <c r="C18" s="22">
-        <v>0.001347758994144415</v>
+        <v>0.0023297849276334532</v>
       </c>
       <c r="D18" s="22">
-        <v>-0.006106186961890438</v>
+        <v>-0.005173262438383082</v>
       </c>
       <c r="E18" s="22">
-        <v>-0.01285023330306481</v>
+        <v>-0.01196173385450173</v>
       </c>
       <c r="F18" s="22">
-        <v>-0.018981184522314284</v>
+        <v>-0.01813307149704626</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2373,19 +2373,19 @@
         <v>102</v>
       </c>
       <c r="B19" s="22">
-        <v>0.014350753606338565</v>
+        <v>0.015418434168108428</v>
       </c>
       <c r="C19" s="22">
-        <v>0.00582012656776532</v>
+        <v>0.00683161327925903</v>
       </c>
       <c r="D19" s="22">
-        <v>-0.001857437766950579</v>
+        <v>-0.0008965255077380014</v>
       </c>
       <c r="E19" s="22">
-        <v>-0.008803805498360183</v>
+        <v>-0.007888651066340208</v>
       </c>
       <c r="F19" s="22">
-        <v>-0.015118685254187136</v>
+        <v>-0.014245128838161075</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2393,19 +2393,19 @@
         <v>103</v>
       </c>
       <c r="B20" s="22">
-        <v>-0.07501241887744438</v>
+        <v>-0.06891925747825473</v>
       </c>
       <c r="C20" s="22">
-        <v>-0.12369597577824995</v>
+        <v>-0.11792350786360487</v>
       </c>
       <c r="D20" s="22">
-        <v>-0.16751117698995086</v>
+        <v>-0.1620273331368475</v>
       </c>
       <c r="E20" s="22">
-        <v>-0.2071535018944534</v>
+        <v>-0.20193079403743108</v>
       </c>
       <c r="F20" s="22">
-        <v>-0.2431919790816075</v>
+        <v>-0.2382066675335976</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2413,19 +2413,19 @@
         <v>104</v>
       </c>
       <c r="B21" s="22">
-        <v>0.002089100422441278</v>
+        <v>0.005471123120289852</v>
       </c>
       <c r="C21" s="22">
-        <v>-0.02532175688568401</v>
+        <v>-0.022034498829739763</v>
       </c>
       <c r="D21" s="22">
-        <v>-0.050616487330710544</v>
+        <v>-0.04741656838258597</v>
       </c>
       <c r="E21" s="22">
-        <v>-0.07405329811797093</v>
+        <v>-0.07093420900259328</v>
       </c>
       <c r="F21" s="22">
-        <v>-0.09584840392527424</v>
+        <v>-0.09280440125254971</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2433,19 +2433,19 @@
         <v>105</v>
       </c>
       <c r="B22" s="22">
-        <v>0.029181591788389548</v>
+        <v>0.03155526133596745</v>
       </c>
       <c r="C22" s="22">
-        <v>0.009857472870357743</v>
+        <v>0.012183101462092298</v>
       </c>
       <c r="D22" s="22">
-        <v>-0.008114285363200139</v>
+        <v>-0.005833177188422375</v>
       </c>
       <c r="E22" s="22">
-        <v>-0.024890233819291455</v>
+        <v>-0.022650547563463026</v>
       </c>
       <c r="F22" s="22">
-        <v>-0.04060232375415781</v>
+        <v>-0.038401314722075336</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2453,19 +2453,19 @@
         <v>106</v>
       </c>
       <c r="B23" s="22">
-        <v>0.04298388103700916</v>
+        <v>0.044833021499594936</v>
       </c>
       <c r="C23" s="22">
-        <v>0.027900081543001914</v>
+        <v>0.029718244830359477</v>
       </c>
       <c r="D23" s="22">
-        <v>0.013822964090587125</v>
+        <v>0.015612403600780856</v>
       </c>
       <c r="E23" s="22">
-        <v>0.0006385611813529686</v>
+        <v>0.0024012583360692764</v>
       </c>
       <c r="F23" s="22">
-        <v>-0.011749417099796773</v>
+        <v>-0.010011708440666303</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2473,19 +2473,19 @@
         <v>107</v>
       </c>
       <c r="B24" s="22">
-        <v>0.05133733736660755</v>
+        <v>0.052865399328568985</v>
       </c>
       <c r="C24" s="22">
-        <v>0.03886021643989716</v>
+        <v>0.04036536584561272</v>
       </c>
       <c r="D24" s="22">
-        <v>0.027195297306015075</v>
+        <v>0.02867923056229956</v>
       </c>
       <c r="E24" s="22">
-        <v>0.01625149473335978</v>
+        <v>0.017715699487961093</v>
       </c>
       <c r="F24" s="22">
-        <v>0.005951793394232841</v>
+        <v>0.007397583230470357</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2493,19 +2493,19 @@
         <v>108</v>
       </c>
       <c r="B25" s="22">
-        <v>-0.3462733025720054</v>
+        <v>-0.3291816857445057</v>
       </c>
       <c r="C25" s="22">
-        <v>-0.4828330694761398</v>
+        <v>-0.46664101361387933</v>
       </c>
       <c r="D25" s="22">
-        <v>-0.6057368596894298</v>
+        <v>-0.5903544084883661</v>
       </c>
       <c r="E25" s="22">
-        <v>-0.7169355270251186</v>
+        <v>-0.7022855751105913</v>
       </c>
       <c r="F25" s="22">
-        <v>-0.8180252246033901</v>
+        <v>-0.8040411809907714</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2513,19 +2513,19 @@
         <v>109</v>
       </c>
       <c r="B26" s="22">
-        <v>-0.12796942281916537</v>
+        <v>-0.1174809898937756</v>
       </c>
       <c r="C26" s="22">
-        <v>-0.21631005241423734</v>
+        <v>-0.2053691384267111</v>
       </c>
       <c r="D26" s="22">
-        <v>-0.30442097301506466</v>
+        <v>-0.29284511423154513</v>
       </c>
       <c r="E26" s="22">
-        <v>-0.3940460272606151</v>
+        <v>-0.3815591124222639</v>
       </c>
       <c r="F26" s="22">
-        <v>-0.4876927271934679</v>
+        <v>-0.47382886882360153</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2533,19 +2533,19 @@
         <v>110</v>
       </c>
       <c r="B27" s="22">
-        <v>-0.04342239289741195</v>
+        <v>-0.036224472130776404</v>
       </c>
       <c r="C27" s="22">
-        <v>-0.10465341123162945</v>
+        <v>-0.09701116991527117</v>
       </c>
       <c r="D27" s="22">
-        <v>-0.16679624805580284</v>
+        <v>-0.15857252802507937</v>
       </c>
       <c r="E27" s="22">
-        <v>-0.23102936745775812</v>
+        <v>-0.2220244763279884</v>
       </c>
       <c r="F27" s="22">
-        <v>-0.2989967924693492</v>
+        <v>-0.2888976487934958</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2553,19 +2553,19 @@
         <v>111</v>
       </c>
       <c r="B28" s="22">
-        <v>-0.00019550150425684968</v>
+        <v>0.005167383014524143</v>
       </c>
       <c r="C28" s="22">
-        <v>-0.04584935583404446</v>
+        <v>-0.040149385114278326</v>
       </c>
       <c r="D28" s="22">
-        <v>-0.09218323147093103</v>
+        <v>-0.08605537881884444</v>
       </c>
       <c r="E28" s="22">
-        <v>-0.13994721556500972</v>
+        <v>-0.13326553499835808</v>
       </c>
       <c r="F28" s="22">
-        <v>-0.19012355484064258</v>
+        <v>-0.18270361661472756</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2573,19 +2573,19 @@
         <v>112</v>
       </c>
       <c r="B29" s="22">
-        <v>0.0252981118196092</v>
+        <v>0.029521037919939905</v>
       </c>
       <c r="C29" s="22">
-        <v>-0.01057437601612131</v>
+        <v>-0.006104123127582522</v>
       </c>
       <c r="D29" s="22">
-        <v>-0.04679763381132661</v>
+        <v>-0.04202009237972533</v>
       </c>
       <c r="E29" s="22">
-        <v>-0.08386309316089216</v>
+        <v>-0.07869872856533722</v>
       </c>
       <c r="F29" s="22">
-        <v>-0.1223740766964464</v>
+        <v>-0.11671288637234604</v>
       </c>
     </row>
   </sheetData>
